--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487811_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487811_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6804</v>
+        <v>6.3446</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7696</v>
+        <v>5.698</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.6466</v>
       </c>
       <c r="G2" t="n">
         <v>5.0316</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1006</v>
+        <v>-0.2352</v>
       </c>
       <c r="T2" t="n">
-        <v>0.773</v>
+        <v>-0.2985</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3276</v>
+        <v>0.0634</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1168</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6387</v>
+        <v>5.7702</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5436</v>
+        <v>3.3491</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0951</v>
+        <v>2.421</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9361</v>
+        <v>5.1749</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7677</v>
+        <v>-0.0959</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1684</v>
+        <v>5.2708</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3607</v>
+        <v>2.9585</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1639</v>
+        <v>-0.1284</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1969</v>
+        <v>3.0869</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5754</v>
+        <v>2.2164</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3962</v>
+        <v>0.0324</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9716</v>
+        <v>2.184</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2494</v>
+        <v>-0.8393</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7854</v>
+        <v>-0.78</v>
       </c>
       <c r="U3" t="n">
-        <v>0.464</v>
+        <v>-0.0593</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0035</v>
+        <v>0.8102</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3975</v>
+        <v>2.2112</v>
       </c>
       <c r="X3" t="n">
         <v>-1.401</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0979</v>
+        <v>5.6053</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7062</v>
+        <v>4.6864</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3917</v>
+        <v>0.919</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1749</v>
+        <v>3.9361</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0959</v>
+        <v>1.7677</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2708</v>
+        <v>2.1684</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9585</v>
+        <v>3.3607</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1284</v>
+        <v>2.1639</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0869</v>
+        <v>1.1969</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2164</v>
+        <v>0.5754</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0324</v>
+        <v>-0.3962</v>
       </c>
       <c r="O4" t="n">
-        <v>2.184</v>
+        <v>0.9716</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5116</v>
+        <v>0.216</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.423</v>
+        <v>-0.0718</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0886</v>
+        <v>0.2878</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8102</v>
+        <v>-0.0035</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2112</v>
+        <v>1.3975</v>
       </c>
       <c r="X4" t="n">
         <v>-1.401</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8544</v>
+        <v>1.1442</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3069</v>
+        <v>0.4793</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5475</v>
+        <v>0.6649</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0934</v>
@@ -844,13 +844,13 @@
         <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2603</v>
+        <v>0.0295</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1957</v>
+        <v>-0.0233</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0646</v>
+        <v>0.0529</v>
       </c>
       <c r="V5" t="n">
         <v>0.5838</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3811</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>0.1427</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5239</v>
+        <v>-0.2303</v>
       </c>
       <c r="G6" t="n">
         <v>1.6782</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0406</v>
+        <v>-0.747</v>
       </c>
       <c r="T6" t="n">
         <v>-0.3948</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6458</v>
+        <v>-0.3522</v>
       </c>
       <c r="V6" t="n">
         <v>0.23</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>I. ALVAREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8115</v>
+        <v>-0.3761</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0425</v>
+        <v>-0.4635</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.769</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4992</v>
+        <v>-0.2045</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7271</v>
+        <v>-0.6078</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2263</v>
+        <v>0.4033</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9362</v>
+        <v>-0.5473</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1431</v>
+        <v>-0.4118</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0793</v>
+        <v>-0.1355</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.437</v>
+        <v>0.3428</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5839</v>
+        <v>-0.196</v>
       </c>
       <c r="O7" t="n">
-        <v>0.147</v>
+        <v>0.5389</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3294</v>
+        <v>0.0939</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9786</v>
+        <v>-0.1462</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6492</v>
+        <v>0.2401</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3975</v>
+        <v>-1.5142</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3975</v>
+        <v>-1.7442</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ALVAREZ FERNANDEZ</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0755</v>
+        <v>-0.6956</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9574</v>
+        <v>0.279</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1181</v>
+        <v>-0.9745</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2045</v>
+        <v>0.4992</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6078</v>
+        <v>-0.7271</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4033</v>
+        <v>1.2263</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5473</v>
+        <v>0.9362</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4118</v>
+        <v>-0.1431</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1355</v>
+        <v>1.0793</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3428</v>
+        <v>-0.437</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.196</v>
+        <v>-0.5839</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5389</v>
+        <v>0.147</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6054</v>
+        <v>-0.2135</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.64</v>
+        <v>-0.6572</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0346</v>
+        <v>0.4437</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5142</v>
+        <v>-1.3975</v>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7442</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.683</v>
+        <v>-1.8574</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6162</v>
+        <v>-2.908</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9332</v>
+        <v>1.0506</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7764</v>
@@ -1156,13 +1156,13 @@
         <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3381</v>
+        <v>-0.5125</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7053</v>
+        <v>0.0029</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6328</v>
+        <v>-0.5153</v>
       </c>
       <c r="V9" t="n">
         <v>-1.401</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4063</v>
+        <v>-2.8141</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.184</v>
+        <v>-2.7973</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2223</v>
+        <v>-0.0168</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2953</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6831</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3915</v>
+        <v>-0.0047</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2916</v>
+        <v>-0.0861</v>
       </c>
       <c r="V10" t="n">
         <v>0.8208</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5186</v>
+        <v>-4.312</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5399</v>
+        <v>-5.0104</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0213</v>
+        <v>0.6984</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7239</v>
@@ -1312,13 +1312,13 @@
         <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1515</v>
+        <v>0.358</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8539</v>
+        <v>0.3834</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2976</v>
+        <v>-0.0254</v>
       </c>
       <c r="V11" t="n">
         <v>0.3432</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.395399999999999</v>
+        <v>8.721599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3.128999999999998</v>
+        <v>3.455300000000002</v>
       </c>
       <c r="F12" t="n">
         <v>5.2663</v>
@@ -1357,13 +1357,13 @@
         <v>10.2265</v>
       </c>
       <c r="H12" t="n">
-        <v>3.613299999999999</v>
+        <v>3.6133</v>
       </c>
       <c r="I12" t="n">
         <v>6.613</v>
       </c>
       <c r="J12" t="n">
-        <v>4.798399999999998</v>
+        <v>4.798400000000002</v>
       </c>
       <c r="K12" t="n">
         <v>4.6557</v>
@@ -1390,13 +1390,13 @@
         <v>11.4465</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.267</v>
+        <v>-1.9409</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3166</v>
+        <v>-1.9902</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04959999999999992</v>
+        <v>0.0496</v>
       </c>
       <c r="V12" t="n">
         <v>-1.645</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3305</v>
+        <v>4.6877</v>
       </c>
       <c r="E13" t="n">
-        <v>3.949</v>
+        <v>4.1633</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3815</v>
+        <v>0.5244</v>
       </c>
       <c r="G13" t="n">
         <v>1.6038</v>
@@ -1468,13 +1468,13 @@
         <v>1.4568</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1024</v>
+        <v>0.4596</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4881</v>
+        <v>-0.2738</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5905</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.1675</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4965</v>
+        <v>1.702</v>
       </c>
       <c r="E14" t="n">
         <v>1.2051</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2914</v>
+        <v>0.4969</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8259</v>
@@ -1546,13 +1546,13 @@
         <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.274</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2519</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3204</v>
+        <v>0.5259</v>
       </c>
       <c r="V14" t="n">
         <v>3.5026</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8105</v>
+        <v>0.4185</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4903</v>
+        <v>2.5975</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6798</v>
+        <v>-2.179</v>
       </c>
       <c r="G15" t="n">
         <v>0.5931999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8416</v>
+        <v>0.4497</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0091</v>
+        <v>0.1162</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8326</v>
+        <v>0.3334</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.019</v>
+        <v>-0.3788</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6927</v>
+        <v>-1.4428</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7117</v>
+        <v>1.064</v>
       </c>
       <c r="G16" t="n">
         <v>0.0484</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4274</v>
+        <v>1.0296</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4378</v>
+        <v>0.6877</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0104</v>
+        <v>0.3419</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>A. BIRD-JELINEK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2773</v>
+        <v>-0.507</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1919</v>
+        <v>-0.3522</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9146</v>
+        <v>-0.1548</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7603</v>
+        <v>0.3673</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8891</v>
+        <v>-0.712</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8711</v>
+        <v>1.0793</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.0041</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6317</v>
+        <v>-0.369</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2711</v>
+        <v>0.3649</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8575</v>
+        <v>0.3713</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2575</v>
+        <v>-0.3431</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6001</v>
+        <v>0.7144</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6723</v>
+        <v>-0.0793</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2915</v>
+        <v>-0.14</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3808</v>
+        <v>0.0607</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3975</v>
+        <v>-1.6275</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8574</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BIRD-JELINEK</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4943</v>
+        <v>-1.485</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1379</v>
+        <v>-1.1919</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3564</v>
+        <v>-0.2931</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3673</v>
+        <v>-1.7603</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.712</v>
+        <v>-0.8891</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0793</v>
+        <v>-0.8711</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0041</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.369</v>
+        <v>-0.6317</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3649</v>
+        <v>-0.2711</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3713</v>
+        <v>-0.8575</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3431</v>
+        <v>-0.2575</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7144</v>
+        <v>-0.6001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.06660000000000001</v>
+        <v>1.4647</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0743</v>
+        <v>0.2915</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1409</v>
+        <v>1.1731</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6275</v>
+        <v>-1.3975</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6275</v>
+        <v>-1.8574</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3693</v>
+        <v>-1.9979</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9858</v>
+        <v>-2.8787</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6166</v>
+        <v>0.8808</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6849</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.06</v>
+        <v>0.3114</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2701</v>
+        <v>0.3772</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3301</v>
+        <v>-0.0659</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>I. MONTERO MECA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0869</v>
+        <v>-2.6467</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9722</v>
+        <v>0.4251</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1147</v>
+        <v>-3.0718</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7403</v>
+        <v>-3.6518</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8528</v>
+        <v>-0.0726</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8875</v>
+        <v>-3.5792</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.332</v>
+        <v>-2.3167</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6568000000000001</v>
+        <v>0.5196</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6752</v>
+        <v>-2.8363</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4083</v>
+        <v>-1.3352</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.196</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2123</v>
+        <v>-0.7429</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5141</v>
+        <v>-0.1197</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3915</v>
+        <v>-0.0533</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1226</v>
+        <v>-0.0665</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1238</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.795</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MONTERO MECA</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0784</v>
+        <v>-2.9401</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2179</v>
+        <v>-2.9722</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.8605</v>
+        <v>0.0321</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6518</v>
+        <v>-1.7403</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0726</v>
+        <v>-0.8528</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.5792</v>
+        <v>-0.8875</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3167</v>
+        <v>-1.332</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5196</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.8363</v>
+        <v>-0.6752</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3352</v>
+        <v>-0.4083</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.196</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7429</v>
+        <v>-0.2123</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2487</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q21" t="n">
+        <v>-1.2487</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.3673</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.3915</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="V21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.2487</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-1.5515</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.6962</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.8552999999999999</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-0.1238</v>
-      </c>
       <c r="W21" t="n">
-        <v>2.795</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.9188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7458</v>
+        <v>-4.5339</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7125</v>
+        <v>-4.8196</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0333</v>
+        <v>0.2857</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1759</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6531</v>
+        <v>-0.4412</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3047</v>
+        <v>-0.4119</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3484</v>
+        <v>-0.0293</v>
       </c>
       <c r="V22" t="n">
         <v>0.1238</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.3955</v>
+        <v>-7.6812</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.266500000000001</v>
+        <v>-5.266400000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1289</v>
+        <v>-2.4148</v>
       </c>
       <c r="G23" t="n">
         <v>-10.2264</v>
@@ -2227,7 +2227,7 @@
         <v>1.0424</v>
       </c>
       <c r="L23" t="n">
-        <v>-6.470300000000001</v>
+        <v>-6.4703</v>
       </c>
       <c r="M23" t="n">
         <v>-4.7984</v>
@@ -2236,7 +2236,7 @@
         <v>-4.6557</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1426999999999998</v>
+        <v>-0.1426999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-2.0813</v>
@@ -2248,13 +2248,13 @@
         <v>9.365399999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2669</v>
+        <v>2.9815</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.04960000000000003</v>
+        <v>-0.04980000000000018</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3166</v>
+        <v>3.0309</v>
       </c>
       <c r="V23" t="n">
         <v>1.6451</v>
